--- a/doanmon/FILE_LOI_4_QUA_DAI.xlsx
+++ b/doanmon/FILE_LOI_4_QUA_DAI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>productCode</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Short Name</t>
   </si>
   <si>
-    <t>Chocolate</t>
+    <t>Birthday Cakes</t>
   </si>
   <si>
     <t>productCode exceeds 100 characters</t>
@@ -50,7 +50,7 @@
     <t>This is a very long cake name that definitely exceeds one hundred characters limit and will cause validation error</t>
   </si>
   <si>
-    <t>Vanilla</t>
+    <t>Wedding Cakes</t>
   </si>
   <si>
     <t>name exceeds 100 characters</t>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Normal Name</t>
+  </si>
+  <si>
+    <t>Cheese Cakes</t>
   </si>
   <si>
     <t>This one is fine</t>
@@ -205,13 +208,13 @@
         <v>22.5</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>20.0</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
